--- a/robotics/github/github-project-list.xlsx
+++ b/robotics/github/github-project-list.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fork opens. Hardware URL is a 404. STEP hashed, not uploaded.</t>
+          <t>Fork is egc365/openarm of enactic/openarm, 0 ahead and 10 behind. egc365/openarm_hardware was never created. STEP hashed, not uploaded.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/robotics/github/github-project-list.xlsx
+++ b/robotics/github/github-project-list.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fork is egc365/openarm of enactic/openarm, 0 ahead and 10 behind. egc365/openarm_hardware was never created. STEP hashed, not uploaded.</t>
+          <t>Fork is egc365/openarm of enactic/openarm, 0 ahead and 10 behind. egc365/openarm_hardware is HTTP 404 and is not the fork. STEP hashed, not compared with the release tar.gz.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
